--- a/src/main/resources/static/Template_import_asset.xlsx
+++ b/src/main/resources/static/Template_import_asset.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hieux\Desktop\Hust-dev\Documents-Asset\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hieux\Desktop\Projects\src\main\resources\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4105FB73-366D-415B-AF10-ACEFCF1CF6F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6584256E-EFE5-4CE4-8FC8-AF19D3F9719A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="ImportAsset" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet3" sheetId="3" state="hidden" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -730,6 +730,38 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -749,10 +781,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -785,34 +813,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1216,211 +1216,211 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:129" s="26" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="35" t="s">
         <v>98</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="35" t="s">
         <v>103</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="35" t="s">
         <v>102</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="33" t="s">
+      <c r="H1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="33" t="s">
+      <c r="I1" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="33" t="s">
+      <c r="J1" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="33" t="s">
+      <c r="K1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="33" t="s">
+      <c r="L1" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="33" t="s">
+      <c r="M1" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="33" t="s">
+      <c r="N1" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="33" t="s">
+      <c r="O1" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="33" t="s">
+      <c r="P1" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="Q1" s="40" t="s">
+      <c r="Q1" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="R1" s="40"/>
-      <c r="S1" s="40"/>
-      <c r="T1" s="40"/>
-      <c r="U1" s="40"/>
-      <c r="V1" s="40"/>
-      <c r="W1" s="40"/>
-      <c r="X1" s="46" t="s">
+      <c r="R1" s="47"/>
+      <c r="S1" s="47"/>
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
+      <c r="V1" s="47"/>
+      <c r="W1" s="47"/>
+      <c r="X1" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="Y1" s="47"/>
-      <c r="Z1" s="47"/>
-      <c r="AA1" s="48"/>
-      <c r="AB1" s="49" t="s">
+      <c r="Y1" s="31"/>
+      <c r="Z1" s="31"/>
+      <c r="AA1" s="32"/>
+      <c r="AB1" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="AC1" s="50"/>
-      <c r="AD1" s="50"/>
-      <c r="AE1" s="50"/>
-      <c r="AF1" s="50"/>
-      <c r="AG1" s="50"/>
-      <c r="AH1" s="50"/>
-      <c r="AI1" s="42" t="s">
+      <c r="AC1" s="34"/>
+      <c r="AD1" s="34"/>
+      <c r="AE1" s="34"/>
+      <c r="AF1" s="34"/>
+      <c r="AG1" s="34"/>
+      <c r="AH1" s="34"/>
+      <c r="AI1" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="AJ1" s="43"/>
-      <c r="AK1" s="43"/>
-      <c r="AL1" s="43"/>
-      <c r="AM1" s="43"/>
-      <c r="AN1" s="43"/>
-      <c r="AO1" s="44" t="s">
+      <c r="AJ1" s="50"/>
+      <c r="AK1" s="50"/>
+      <c r="AL1" s="50"/>
+      <c r="AM1" s="50"/>
+      <c r="AN1" s="50"/>
+      <c r="AO1" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="AP1" s="45"/>
-      <c r="AQ1" s="45"/>
-      <c r="AR1" s="45"/>
-      <c r="AS1" s="45"/>
-      <c r="AT1" s="45"/>
-      <c r="AU1" s="45"/>
-      <c r="AV1" s="45"/>
-      <c r="AW1" s="45"/>
-      <c r="AX1" s="45"/>
-      <c r="AY1" s="45"/>
-      <c r="AZ1" s="45"/>
-      <c r="BA1" s="45"/>
-      <c r="BB1" s="45"/>
-      <c r="BC1" s="45"/>
-      <c r="BD1" s="45"/>
-      <c r="BE1" s="45"/>
-      <c r="BF1" s="45"/>
-      <c r="BG1" s="45"/>
-      <c r="BH1" s="45"/>
-      <c r="BI1" s="45"/>
-      <c r="BJ1" s="29" t="s">
+      <c r="AP1" s="29"/>
+      <c r="AQ1" s="29"/>
+      <c r="AR1" s="29"/>
+      <c r="AS1" s="29"/>
+      <c r="AT1" s="29"/>
+      <c r="AU1" s="29"/>
+      <c r="AV1" s="29"/>
+      <c r="AW1" s="29"/>
+      <c r="AX1" s="29"/>
+      <c r="AY1" s="29"/>
+      <c r="AZ1" s="29"/>
+      <c r="BA1" s="29"/>
+      <c r="BB1" s="29"/>
+      <c r="BC1" s="29"/>
+      <c r="BD1" s="29"/>
+      <c r="BE1" s="29"/>
+      <c r="BF1" s="29"/>
+      <c r="BG1" s="29"/>
+      <c r="BH1" s="29"/>
+      <c r="BI1" s="29"/>
+      <c r="BJ1" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="BK1" s="30"/>
-      <c r="BL1" s="30"/>
-      <c r="BM1" s="30"/>
-      <c r="BN1" s="30"/>
-      <c r="BO1" s="30"/>
-      <c r="BP1" s="30"/>
-      <c r="BQ1" s="30"/>
-      <c r="BR1" s="30"/>
-      <c r="BS1" s="30"/>
-      <c r="BT1" s="30"/>
-      <c r="BU1" s="30"/>
-      <c r="BV1" s="30"/>
-      <c r="BW1" s="30"/>
-      <c r="BX1" s="30"/>
-      <c r="BY1" s="30"/>
-      <c r="BZ1" s="30"/>
-      <c r="CA1" s="30"/>
-      <c r="CB1" s="31" t="s">
+      <c r="BK1" s="38"/>
+      <c r="BL1" s="38"/>
+      <c r="BM1" s="38"/>
+      <c r="BN1" s="38"/>
+      <c r="BO1" s="38"/>
+      <c r="BP1" s="38"/>
+      <c r="BQ1" s="38"/>
+      <c r="BR1" s="38"/>
+      <c r="BS1" s="38"/>
+      <c r="BT1" s="38"/>
+      <c r="BU1" s="38"/>
+      <c r="BV1" s="38"/>
+      <c r="BW1" s="38"/>
+      <c r="BX1" s="38"/>
+      <c r="BY1" s="38"/>
+      <c r="BZ1" s="38"/>
+      <c r="CA1" s="38"/>
+      <c r="CB1" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="CC1" s="32"/>
-      <c r="CD1" s="32"/>
-      <c r="CE1" s="34" t="s">
+      <c r="CC1" s="40"/>
+      <c r="CD1" s="40"/>
+      <c r="CE1" s="41" t="s">
         <v>99</v>
       </c>
-      <c r="CF1" s="35"/>
-      <c r="CG1" s="35"/>
-      <c r="CH1" s="35"/>
-      <c r="CI1" s="35"/>
-      <c r="CJ1" s="35"/>
-      <c r="CK1" s="36" t="s">
+      <c r="CF1" s="42"/>
+      <c r="CG1" s="42"/>
+      <c r="CH1" s="42"/>
+      <c r="CI1" s="42"/>
+      <c r="CJ1" s="42"/>
+      <c r="CK1" s="43" t="s">
         <v>100</v>
       </c>
-      <c r="CL1" s="37"/>
-      <c r="CM1" s="37"/>
-      <c r="CN1" s="37"/>
-      <c r="CO1" s="37"/>
-      <c r="CP1" s="37"/>
-      <c r="CQ1" s="37"/>
-      <c r="CR1" s="37"/>
-      <c r="CS1" s="37"/>
-      <c r="CT1" s="37"/>
-      <c r="CU1" s="41" t="s">
+      <c r="CL1" s="44"/>
+      <c r="CM1" s="44"/>
+      <c r="CN1" s="44"/>
+      <c r="CO1" s="44"/>
+      <c r="CP1" s="44"/>
+      <c r="CQ1" s="44"/>
+      <c r="CR1" s="44"/>
+      <c r="CS1" s="44"/>
+      <c r="CT1" s="44"/>
+      <c r="CU1" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="CV1" s="41"/>
-      <c r="CW1" s="41"/>
-      <c r="CX1" s="41"/>
-      <c r="CY1" s="41"/>
-      <c r="CZ1" s="41"/>
-      <c r="DA1" s="41"/>
-      <c r="DB1" s="41"/>
-      <c r="DC1" s="41"/>
-      <c r="DD1" s="40" t="s">
+      <c r="CV1" s="48"/>
+      <c r="CW1" s="48"/>
+      <c r="CX1" s="48"/>
+      <c r="CY1" s="48"/>
+      <c r="CZ1" s="48"/>
+      <c r="DA1" s="48"/>
+      <c r="DB1" s="48"/>
+      <c r="DC1" s="48"/>
+      <c r="DD1" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="DE1" s="40"/>
-      <c r="DF1" s="40"/>
-      <c r="DG1" s="40"/>
-      <c r="DH1" s="40"/>
-      <c r="DI1" s="40"/>
-      <c r="DJ1" s="40"/>
-      <c r="DK1" s="38" t="s">
+      <c r="DE1" s="47"/>
+      <c r="DF1" s="47"/>
+      <c r="DG1" s="47"/>
+      <c r="DH1" s="47"/>
+      <c r="DI1" s="47"/>
+      <c r="DJ1" s="47"/>
+      <c r="DK1" s="45" t="s">
         <v>77</v>
       </c>
-      <c r="DL1" s="39"/>
-      <c r="DM1" s="39"/>
-      <c r="DN1" s="39"/>
-      <c r="DO1" s="39"/>
-      <c r="DP1" s="28" t="s">
+      <c r="DL1" s="46"/>
+      <c r="DM1" s="46"/>
+      <c r="DN1" s="46"/>
+      <c r="DO1" s="46"/>
+      <c r="DP1" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="DQ1" s="28"/>
-      <c r="DR1" s="28"/>
-      <c r="DS1" s="28"/>
-      <c r="DT1" s="28"/>
-      <c r="DU1" s="28"/>
-      <c r="DV1" s="28"/>
-      <c r="DW1" s="28"/>
-      <c r="DX1" s="28"/>
-      <c r="DY1" s="28"/>
+      <c r="DQ1" s="36"/>
+      <c r="DR1" s="36"/>
+      <c r="DS1" s="36"/>
+      <c r="DT1" s="36"/>
+      <c r="DU1" s="36"/>
+      <c r="DV1" s="36"/>
+      <c r="DW1" s="36"/>
+      <c r="DX1" s="36"/>
+      <c r="DY1" s="36"/>
     </row>
     <row r="2" spans="1:129" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="33"/>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
+      <c r="A2" s="35"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
       <c r="Q2" s="2" t="s">
         <v>14</v>
       </c>
@@ -1763,19 +1763,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="AO1:BI1"/>
-    <mergeCell ref="X1:AA1"/>
-    <mergeCell ref="AB1:AH1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:J2"/>
     <mergeCell ref="DP1:DY1"/>
     <mergeCell ref="BJ1:CA1"/>
     <mergeCell ref="CB1:CD1"/>
@@ -1792,6 +1779,19 @@
     <mergeCell ref="CU1:DC1"/>
     <mergeCell ref="DD1:DJ1"/>
     <mergeCell ref="AI1:AN1"/>
+    <mergeCell ref="AO1:BI1"/>
+    <mergeCell ref="X1:AA1"/>
+    <mergeCell ref="AB1:AH1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1804,15 +1804,15 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
     </row>
     <row r="2" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
